--- a/map/railway/routes.xlsx
+++ b/map/railway/routes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Unida\Documents\VSC\Python\EpidemicSimulation\map\railway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7417401A-D454-4A54-B8F4-7A61875B3702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADFB6BB-AAC2-4669-A0B3-14696DA9475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4B7EC76-40DE-4591-990E-74C90B15E85F}"/>
+    <workbookView xWindow="24300" yWindow="588" windowWidth="21600" windowHeight="11232" xr2:uid="{D4B7EC76-40DE-4591-990E-74C90B15E85F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Node 1</t>
   </si>
@@ -51,19 +51,30 @@
   </si>
   <si>
     <t>12,13,14</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Peak Interval</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -86,8 +97,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,10 +416,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8EB279B-C5CD-4D36-BA3C-309189E71B1C}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,8 +429,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>23</v>
       </c>
@@ -426,8 +446,14 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>165</v>
       </c>
@@ -436,9 +462,16 @@
       </c>
       <c r="C3" t="s">
         <v>4</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/map/railway/routes.xlsx
+++ b/map/railway/routes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Unida\Documents\VSC\Python\EpidemicSimulation\map\railway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADFB6BB-AAC2-4669-A0B3-14696DA9475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09E6D2E-9C19-41E5-8D3B-072B349DF9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24300" yWindow="588" windowWidth="21600" windowHeight="11232" xr2:uid="{D4B7EC76-40DE-4591-990E-74C90B15E85F}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4B7EC76-40DE-4591-990E-74C90B15E85F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,10 +447,10 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -467,7 +467,7 @@
         <v>12</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
